--- a/data/trans_bre/P16A12-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A12-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,58; -0,84</t>
+          <t>-5,66; -0,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 2,53</t>
+          <t>-3,39; 2,74</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,33; -0,67</t>
+          <t>-7,15; -0,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,22; -2,18</t>
+          <t>-7,17; -2,42</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-89,26; -9,58</t>
+          <t>-90,5; -13,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-62,83; 89,95</t>
+          <t>-60,95; 91,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-76,91; -4,6</t>
+          <t>-76,22; 1,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-74,96; -33,09</t>
+          <t>-74,58; -35,19</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,67; -0,67</t>
+          <t>-5,85; -0,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 0,54</t>
+          <t>-5,46; 0,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,57; -0,54</t>
+          <t>-6,12; -0,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,93; -4,32</t>
+          <t>-9,98; -4,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-89,89; -8,65</t>
+          <t>-91,64; -10,63</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-79,01; 24,04</t>
+          <t>-80,03; 26,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-83,21; -1,89</t>
+          <t>-81,31; 1,6</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-84,8; -55,41</t>
+          <t>-85,9; -55,69</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 7,16</t>
+          <t>-1,66; 7,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 0,32</t>
+          <t>-7,95; 0,16</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 1,98</t>
+          <t>-7,85; 1,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,46; 9,92</t>
+          <t>-2,52; 11,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-35,58; 177,95</t>
+          <t>-27,86; 164,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-66,11; 7,48</t>
+          <t>-67,12; 2,87</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-70,87; 25,51</t>
+          <t>-69,54; 22,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-23,16; 322,81</t>
+          <t>-22,56; 334,79</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,18; -1,02</t>
+          <t>-5,1; -1,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,29; -1,52</t>
+          <t>-6,11; -1,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,65; -3,32</t>
+          <t>-7,76; -3,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,32; -4,23</t>
+          <t>-9,26; -4,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,39; -14,99</t>
+          <t>-61,0; -15,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-61,61; -17,15</t>
+          <t>-60,61; -15,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-74,41; -40,02</t>
+          <t>-74,04; -41,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-80,09; -43,97</t>
+          <t>-81,45; -43,67</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 1,93</t>
+          <t>-4,41; 1,97</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 4,8</t>
+          <t>-1,1; 5,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 2,12</t>
+          <t>-4,75; 1,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 3,97</t>
+          <t>-2,35; 4,07</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-52,84; 41,05</t>
+          <t>-52,21; 50,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,1; 91,38</t>
+          <t>-15,21; 103,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-38,99; 23,89</t>
+          <t>-38,86; 21,84</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,98; 54,97</t>
+          <t>-21,55; 55,92</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,79; 11,37</t>
+          <t>7,72; 11,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,65; 14,26</t>
+          <t>8,71; 14,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,24; 14,4</t>
+          <t>9,44; 14,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,3; 12,23</t>
+          <t>8,06; 12,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>148,49; 1769,41</t>
+          <t>174,29; 1817,18</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>281,52; 3738,84</t>
+          <t>279,6; 3380,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>319,76; 5965,75</t>
+          <t>283,42; 5512,21</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,53</t>
+          <t>-0,69; 1,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 2,52</t>
+          <t>-0,22; 2,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,81</t>
+          <t>-1,91; 0,73</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 0,86</t>
+          <t>-2,79; 0,61</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,82; 30,65</t>
+          <t>-11,01; 33,13</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 38,05</t>
+          <t>-2,88; 38,08</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-22,72; 10,43</t>
+          <t>-21,18; 9,57</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-31,54; 9,87</t>
+          <t>-31,07; 7,67</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A12-Clase-trans_bre.xlsx
+++ b/data/trans_bre/P16A12-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-4,65</t>
+          <t>-4,58</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-59,91%</t>
+          <t>-59,89%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,66; -0,86</t>
+          <t>-5,65; -1,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 2,74</t>
+          <t>-3,46; 2,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,15; -0,3</t>
+          <t>-7,25; -0,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,17; -2,42</t>
+          <t>-7,29; -2,44</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-90,5; -13,61</t>
+          <t>-89,5; -14,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-60,95; 91,89</t>
+          <t>-62,65; 83,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-76,22; 1,4</t>
+          <t>-76,59; -1,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-74,58; -35,19</t>
+          <t>-76,02; -37,7</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-6,85</t>
+          <t>-6,36</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-73,98%</t>
+          <t>-71,53%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,85; -0,78</t>
+          <t>-5,33; -0,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 0,69</t>
+          <t>-5,59; 0,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-6,12; -0,48</t>
+          <t>-6,72; -0,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-9,98; -4,37</t>
+          <t>-9,27; -3,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-91,64; -10,63</t>
+          <t>-90,36; -4,06</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-80,03; 26,63</t>
+          <t>-80,75; 9,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-81,31; 1,6</t>
+          <t>-82,87; -4,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-85,9; -55,69</t>
+          <t>-83,86; -51,41</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,99</t>
+          <t>-0,5</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>-4,86%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 7,18</t>
+          <t>-1,72; 7,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,95; 0,16</t>
+          <t>-8,04; 0,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 1,81</t>
+          <t>-7,77; 2,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 11,06</t>
+          <t>-4,57; 3,78</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-27,86; 164,01</t>
+          <t>-31,94; 168,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-67,12; 2,87</t>
+          <t>-67,06; 4,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-69,54; 22,19</t>
+          <t>-69,59; 34,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-22,56; 334,79</t>
+          <t>-38,96; 43,54</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-6,28</t>
+          <t>-5,52</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-59,76%</t>
+          <t>-51,44%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-5,1; -1,03</t>
+          <t>-5,18; -1,09</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-6,11; -1,17</t>
+          <t>-6,09; -1,48</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-7,76; -3,47</t>
+          <t>-7,81; -3,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-9,26; -4,23</t>
+          <t>-7,73; -3,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-61,0; -15,3</t>
+          <t>-62,15; -15,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-60,61; -15,17</t>
+          <t>-61,0; -16,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-74,04; -41,06</t>
+          <t>-75,47; -41,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-81,45; -43,67</t>
+          <t>-63,89; -36,19</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,14</t>
+          <t>2,84</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -1060,49 +1060,49 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 1,97</t>
+          <t>-4,91; 1,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 5,13</t>
+          <t>-1,08; 5,19</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 1,91</t>
+          <t>-4,85; 1,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 4,07</t>
+          <t>0,23; 5,39</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-52,21; 50,47</t>
+          <t>-56,42; 35,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 103,57</t>
+          <t>-14,18; 104,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-38,86; 21,84</t>
+          <t>-40,39; 18,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-21,55; 55,92</t>
+          <t>1,32; 83,33</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>10,26</t>
+          <t>10,0</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>1220,63%</t>
+          <t>1178,21%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,72; 11,3</t>
+          <t>7,83; 11,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8,71; 14,38</t>
+          <t>8,82; 14,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,44; 14,54</t>
+          <t>9,48; 14,68</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8,06; 12,1</t>
+          <t>7,96; 11,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>174,29; 1817,18</t>
+          <t>169,91; 1814,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>279,6; 3380,15</t>
+          <t>278,31; 3710,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>283,42; 5512,21</t>
+          <t>350,03; 4902,68</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-1,32</t>
+          <t>-1,34</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-15,87%</t>
+          <t>-15,17%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,65</t>
+          <t>-0,66; 1,6</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 2,54</t>
+          <t>-0,19; 2,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,73</t>
+          <t>-1,95; 0,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,61</t>
+          <t>-2,48; -0,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-11,01; 33,13</t>
+          <t>-10,74; 31,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,88; 38,08</t>
+          <t>-2,17; 42,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-21,18; 9,57</t>
+          <t>-20,89; 9,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-31,07; 7,67</t>
+          <t>-25,95; -3,23</t>
         </is>
       </c>
     </row>
